--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Family_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Family_by_Sample_Type.xlsx
@@ -501,10 +501,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -515,10 +515,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -529,10 +529,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>12.4378584460888</v>
+        <v>12.4382553298214</v>
       </c>
       <c r="D4" t="n">
-        <v>0.428313229449437</v>
+        <v>0.428325745678215</v>
       </c>
     </row>
     <row r="5">
@@ -543,10 +543,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -557,10 +557,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -571,10 +571,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -585,10 +585,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -599,10 +599,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.83589091559257</v>
+        <v>3.83683841548952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0623380318541722</v>
+        <v>0.0623643528173048</v>
       </c>
     </row>
     <row r="10">
@@ -613,10 +613,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.11433185157042</v>
+        <v>3.11454051303145</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0384232790596677</v>
+        <v>0.0384252193784699</v>
       </c>
     </row>
     <row r="11">
@@ -627,10 +627,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -641,10 +641,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.32056948721848</v>
+        <v>1.32060121834943</v>
       </c>
       <c r="D12" t="n">
-        <v>0.355227968619002</v>
+        <v>0.35523739701465</v>
       </c>
     </row>
     <row r="13">
@@ -655,10 +655,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="14">
@@ -669,10 +669,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="15">
@@ -683,10 +683,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D15" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="16">
@@ -697,10 +697,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.642172015204204</v>
+        <v>0.642169123069737</v>
       </c>
       <c r="D16" t="n">
-        <v>0.165207216080162</v>
+        <v>0.165199823432465</v>
       </c>
     </row>
     <row r="17">
@@ -711,10 +711,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618749698372989</v>
+        <v>0.618964822119536</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0592935207008076</v>
+        <v>0.0593170263818895</v>
       </c>
     </row>
     <row r="18">
@@ -725,10 +725,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.491137416768517</v>
+        <v>0.491332939185717</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0357046963386505</v>
+        <v>0.0357189445714107</v>
       </c>
     </row>
     <row r="19">
@@ -739,10 +739,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.357265870418504</v>
+        <v>0.35731527246983</v>
       </c>
       <c r="D19" t="n">
-        <v>0.152724159139168</v>
+        <v>0.152749757190219</v>
       </c>
     </row>
     <row r="20">
@@ -753,10 +753,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.296817331957364</v>
+        <v>0.296857210085557</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0534516862568478</v>
+        <v>0.0534584442625477</v>
       </c>
     </row>
     <row r="21">
@@ -767,10 +767,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="D21" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="22">
@@ -781,7 +781,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="D22"/>
     </row>
@@ -793,10 +793,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.146974458714768</v>
+        <v>0.146966996070451</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0129045399311217</v>
+        <v>0.0129042651403242</v>
       </c>
     </row>
     <row r="24">
@@ -807,10 +807,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="25">
@@ -821,10 +821,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="26">
@@ -835,10 +835,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D26" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="27">
@@ -849,10 +849,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="28">
@@ -863,7 +863,7 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="D28"/>
     </row>
@@ -875,10 +875,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0577451720243945</v>
+        <v>0.0577727984075593</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00615561606809399</v>
+        <v>0.00615693902785514</v>
       </c>
     </row>
     <row r="30">
@@ -889,7 +889,7 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D30"/>
     </row>
@@ -901,7 +901,7 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D31"/>
     </row>
@@ -913,10 +913,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.015787218129565</v>
+        <v>0.0157889711102967</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00588204337348365</v>
+        <v>0.00588424684009715</v>
       </c>
     </row>
     <row r="33">
@@ -927,10 +927,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00727727790575996</v>
+        <v>0.00727632488319893</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0014999434261184</v>
+        <v>0.00149874617041298</v>
       </c>
     </row>
     <row r="34">
@@ -941,7 +941,7 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="D34"/>
     </row>
@@ -953,7 +953,7 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="D35"/>
     </row>
@@ -965,7 +965,7 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D36"/>
     </row>
@@ -977,7 +977,7 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00119930614215706</v>
+        <v>0.00119886362192086</v>
       </c>
       <c r="D37"/>
     </row>
@@ -1014,10 +1014,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>54.1129255454368</v>
+        <v>54.2903931518093</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2494138186117</v>
+        <v>10.2900236788944</v>
       </c>
     </row>
     <row r="3">
@@ -1028,10 +1028,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>14.0113828332472</v>
+        <v>13.9750635903223</v>
       </c>
       <c r="D3" t="n">
-        <v>0.278198742117243</v>
+        <v>0.277431723380653</v>
       </c>
     </row>
     <row r="4">
@@ -1042,10 +1042,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>5.60580054516845</v>
+        <v>5.56924494107659</v>
       </c>
       <c r="D4" t="n">
-        <v>0.580672928149858</v>
+        <v>0.578594848887287</v>
       </c>
     </row>
     <row r="5">
@@ -1056,10 +1056,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>5.16558214826172</v>
+        <v>5.15395900261956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.138750456740007</v>
+        <v>0.138392216828981</v>
       </c>
     </row>
     <row r="6">
@@ -1070,10 +1070,10 @@
         <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>3.7854109959605</v>
+        <v>3.7776036435902</v>
       </c>
       <c r="D6" t="n">
-        <v>0.281556330293027</v>
+        <v>0.280887077483567</v>
       </c>
     </row>
     <row r="7">
@@ -1084,10 +1084,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>3.06739139740554</v>
+        <v>3.01882625814057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.444867388771745</v>
+        <v>0.434510459085714</v>
       </c>
     </row>
     <row r="8">
@@ -1098,10 +1098,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>2.38068014178256</v>
+        <v>2.37341644833467</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0576789885094573</v>
+        <v>0.0575256732831891</v>
       </c>
     </row>
     <row r="9">
@@ -1112,10 +1112,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3714300919777</v>
+        <v>2.36654661741218</v>
       </c>
       <c r="D9" t="n">
-        <v>0.619525480262922</v>
+        <v>0.618148293180579</v>
       </c>
     </row>
     <row r="10">
@@ -1126,10 +1126,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>2.24205641976126</v>
+        <v>2.23606017651098</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0713753178321541</v>
+        <v>0.0711594274333986</v>
       </c>
     </row>
     <row r="11">
@@ -1140,10 +1140,10 @@
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>1.48665146850221</v>
+        <v>1.48241692400949</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0487943680005873</v>
+        <v>0.0486365079780662</v>
       </c>
     </row>
     <row r="12">
@@ -1154,10 +1154,10 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>1.44257685920316</v>
+        <v>1.43906660564869</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0493847440262116</v>
+        <v>0.0492352887412829</v>
       </c>
     </row>
     <row r="13">
@@ -1168,10 +1168,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>1.32716241454733</v>
+        <v>1.3240618689994</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0559850266460437</v>
+        <v>0.055841320783689</v>
       </c>
     </row>
     <row r="14">
@@ -1182,10 +1182,10 @@
         <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>0.751673776876524</v>
+        <v>0.750074310901611</v>
       </c>
       <c r="D14" t="n">
-        <v>0.115842844679538</v>
+        <v>0.115409103286247</v>
       </c>
     </row>
     <row r="15">
@@ -1196,10 +1196,10 @@
         <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>0.509258253215987</v>
+        <v>0.508486644638778</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0463705023945219</v>
+        <v>0.0462714911307914</v>
       </c>
     </row>
     <row r="16">
@@ -1210,10 +1210,10 @@
         <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>0.414671739225594</v>
+        <v>0.413506225981547</v>
       </c>
       <c r="D16" t="n">
-        <v>0.201833006226954</v>
+        <v>0.201264866894501</v>
       </c>
     </row>
     <row r="17">
@@ -1224,10 +1224,10 @@
         <v>34</v>
       </c>
       <c r="C17" t="n">
-        <v>0.351612305902911</v>
+        <v>0.351483052903812</v>
       </c>
       <c r="D17" t="n">
-        <v>0.155646830278538</v>
+        <v>0.155638374117642</v>
       </c>
     </row>
     <row r="18">
@@ -1238,10 +1238,10 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>0.292759321588185</v>
+        <v>0.292113835287215</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0314484441060364</v>
+        <v>0.0313858424067945</v>
       </c>
     </row>
     <row r="19">
@@ -1252,10 +1252,10 @@
         <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>0.202909538947346</v>
+        <v>0.200269945495604</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0110467151095926</v>
+        <v>0.0107855099896259</v>
       </c>
     </row>
     <row r="20">
@@ -1266,10 +1266,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.18885004415727</v>
+        <v>0.188888925600684</v>
       </c>
       <c r="D20" t="n">
-        <v>0.081184499936407</v>
+        <v>0.0812062953531732</v>
       </c>
     </row>
     <row r="21">
@@ -1280,7 +1280,7 @@
         <v>31</v>
       </c>
       <c r="C21" t="n">
-        <v>0.122043620490263</v>
+        <v>0.121669959620492</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1292,10 +1292,10 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>0.031028231306782</v>
+        <v>0.0309894801565336</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00584097358048779</v>
+        <v>0.00583147820982544</v>
       </c>
     </row>
     <row r="23">
@@ -1306,7 +1306,7 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0296149408341879</v>
+        <v>0.0295685255181075</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1318,10 +1318,10 @@
         <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0245626860204542</v>
+        <v>0.0245125083963238</v>
       </c>
       <c r="D24" t="n">
-        <v>0.004710844758253</v>
+        <v>0.00470171081027407</v>
       </c>
     </row>
     <row r="25">
@@ -1332,10 +1332,10 @@
         <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0214075508501126</v>
+        <v>0.0213649759054163</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00582731581784547</v>
+        <v>0.00581331564038483</v>
       </c>
     </row>
     <row r="26">
@@ -1346,10 +1346,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0112981671212124</v>
+        <v>0.0112786167875188</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00220970538097561</v>
+        <v>0.00220594438459289</v>
       </c>
     </row>
     <row r="27">
@@ -1360,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="n">
-        <v>0.010897695032061</v>
+        <v>0.0108696982802279</v>
       </c>
       <c r="D27"/>
     </row>
@@ -1372,7 +1372,7 @@
         <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00848451746553975</v>
+        <v>0.00846763661958161</v>
       </c>
       <c r="D28"/>
     </row>
@@ -1384,7 +1384,7 @@
         <v>37</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00774464876233345</v>
+        <v>0.00771820051894665</v>
       </c>
       <c r="D29"/>
     </row>
@@ -1396,10 +1396,10 @@
         <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0041750160272889</v>
+        <v>0.00416640871343739</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00180723739682924</v>
+        <v>0.00180506113275028</v>
       </c>
     </row>
     <row r="31">
@@ -1410,10 +1410,10 @@
         <v>35</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00356565387673206</v>
+        <v>0.00355446836301152</v>
       </c>
       <c r="D31" t="n">
-        <v>0.000994705038762322</v>
+        <v>0.000992009054043805</v>
       </c>
     </row>
     <row r="32">
@@ -1424,7 +1424,7 @@
         <v>33</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00336541783215633</v>
+        <v>0.00335957532414269</v>
       </c>
       <c r="D32"/>
     </row>
@@ -1436,7 +1436,7 @@
         <v>42</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00333010546463304</v>
+        <v>0.00331873303929328</v>
       </c>
       <c r="D33"/>
     </row>
@@ -1448,7 +1448,7 @@
         <v>27</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00251404162474268</v>
+        <v>0.0025108092006458</v>
       </c>
       <c r="D34"/>
     </row>
@@ -1460,7 +1460,7 @@
         <v>43</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00214639511666921</v>
+        <v>0.00214104773829548</v>
       </c>
       <c r="D35"/>
     </row>
@@ -1472,7 +1472,7 @@
         <v>30</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00161919639026515</v>
+        <v>0.0016136667785894</v>
       </c>
       <c r="D36"/>
     </row>
@@ -1484,7 +1484,7 @@
         <v>44</v>
       </c>
       <c r="C37" t="n">
-        <v>0.000961590582669442</v>
+        <v>0.000959892825720676</v>
       </c>
       <c r="D37"/>
     </row>
@@ -1496,7 +1496,7 @@
         <v>45</v>
       </c>
       <c r="C38" t="n">
-        <v>0.000454684033659048</v>
+        <v>0.000453626930754705</v>
       </c>
       <c r="D38"/>
     </row>
